--- a/artfynd/A 16246-2024 artfynd.xlsx
+++ b/artfynd/A 16246-2024 artfynd.xlsx
@@ -889,48 +889,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128534788</v>
+        <v>128537013</v>
       </c>
       <c r="B4" t="n">
-        <v>92754</v>
+        <v>57845</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446383</v>
+        <v>446498</v>
       </c>
       <c r="R4" t="n">
-        <v>6948178</v>
+        <v>6948254</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,65 +989,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128537013</v>
+        <v>128534788</v>
       </c>
       <c r="B5" t="n">
-        <v>57845</v>
+        <v>92754</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446498</v>
+        <v>446383</v>
       </c>
       <c r="R5" t="n">
-        <v>6948254</v>
+        <v>6948178</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,12 +1096,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128536962</v>
+        <v>128535657</v>
       </c>
       <c r="B7" t="n">
-        <v>78840</v>
+        <v>57685</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,34 +1226,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446532</v>
+        <v>446810</v>
       </c>
       <c r="R7" t="n">
-        <v>6948261</v>
+        <v>6948241</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1300,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128535657</v>
+        <v>128536962</v>
       </c>
       <c r="B8" t="n">
-        <v>57685</v>
+        <v>78840</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,39 +1343,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446810</v>
+        <v>446532</v>
       </c>
       <c r="R8" t="n">
-        <v>6948241</v>
+        <v>6948261</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,12 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2111,7 +2111,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128535281</v>
+        <v>128534949</v>
       </c>
       <c r="B15" t="n">
         <v>57685</v>
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446670</v>
+        <v>446459</v>
       </c>
       <c r="R15" t="n">
-        <v>6948128</v>
+        <v>6948172</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2228,7 +2228,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128534949</v>
+        <v>128535281</v>
       </c>
       <c r="B16" t="n">
         <v>57685</v>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446459</v>
+        <v>446670</v>
       </c>
       <c r="R16" t="n">
-        <v>6948172</v>
+        <v>6948128</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2345,32 +2345,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128535194</v>
+        <v>128536769</v>
       </c>
       <c r="B17" t="n">
-        <v>78840</v>
+        <v>80217</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2380,13 +2380,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446523</v>
+        <v>446993</v>
       </c>
       <c r="R17" t="n">
-        <v>6948226</v>
+        <v>6948000</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2440,44 +2440,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128536398</v>
+        <v>128535194</v>
       </c>
       <c r="B18" t="n">
-        <v>92742</v>
+        <v>78840</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2487,13 +2487,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447199</v>
+        <v>446523</v>
       </c>
       <c r="R18" t="n">
-        <v>6948067</v>
+        <v>6948226</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2547,44 +2547,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128535206</v>
+        <v>128536398</v>
       </c>
       <c r="B19" t="n">
-        <v>92736</v>
+        <v>92742</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2594,13 +2594,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446523</v>
+        <v>447199</v>
       </c>
       <c r="R19" t="n">
-        <v>6948226</v>
+        <v>6948067</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2654,44 +2654,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128536769</v>
+        <v>128535206</v>
       </c>
       <c r="B20" t="n">
-        <v>80217</v>
+        <v>92736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>4362</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2701,13 +2701,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446993</v>
+        <v>446523</v>
       </c>
       <c r="R20" t="n">
-        <v>6948000</v>
+        <v>6948226</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2761,22 +2761,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128534979</v>
+        <v>128536454</v>
       </c>
       <c r="B21" t="n">
-        <v>78840</v>
+        <v>80188</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2784,21 +2784,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446445</v>
+        <v>447211</v>
       </c>
       <c r="R21" t="n">
-        <v>6948176</v>
+        <v>6948028</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2868,22 +2868,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128536454</v>
+        <v>128534979</v>
       </c>
       <c r="B22" t="n">
-        <v>80188</v>
+        <v>78840</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2891,21 +2891,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447211</v>
+        <v>446445</v>
       </c>
       <c r="R22" t="n">
-        <v>6948028</v>
+        <v>6948176</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2975,12 +2975,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3795,32 +3795,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128535425</v>
+        <v>128536760</v>
       </c>
       <c r="B30" t="n">
-        <v>92754</v>
+        <v>80188</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4366</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446718</v>
+        <v>446997</v>
       </c>
       <c r="R30" t="n">
-        <v>6948094</v>
+        <v>6947997</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3902,32 +3902,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128536760</v>
+        <v>128535425</v>
       </c>
       <c r="B31" t="n">
-        <v>80188</v>
+        <v>92754</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446997</v>
+        <v>446718</v>
       </c>
       <c r="R31" t="n">
-        <v>6947997</v>
+        <v>6948094</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 16246-2024 artfynd.xlsx
+++ b/artfynd/A 16246-2024 artfynd.xlsx
@@ -889,53 +889,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128537013</v>
+        <v>128534788</v>
       </c>
       <c r="B4" t="n">
-        <v>57845</v>
+        <v>92754</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446498</v>
+        <v>446383</v>
       </c>
       <c r="R4" t="n">
-        <v>6948254</v>
+        <v>6948178</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,60 +984,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128534788</v>
+        <v>128537013</v>
       </c>
       <c r="B5" t="n">
-        <v>92754</v>
+        <v>57845</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446383</v>
+        <v>446498</v>
       </c>
       <c r="R5" t="n">
-        <v>6948178</v>
+        <v>6948254</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,12 +1096,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1439,48 +1439,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128536758</v>
+        <v>128535023</v>
       </c>
       <c r="B9" t="n">
-        <v>92742</v>
+        <v>57685</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Högflon, Jmt</t>
+          <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446993</v>
+        <v>446481</v>
       </c>
       <c r="R9" t="n">
-        <v>6947982</v>
+        <v>6948165</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,7 +1514,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1524,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,22 +1544,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128535023</v>
+        <v>128536490</v>
       </c>
       <c r="B10" t="n">
-        <v>57685</v>
+        <v>80188</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,39 +1567,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446481</v>
+        <v>447202</v>
       </c>
       <c r="R10" t="n">
-        <v>6948165</v>
+        <v>6948032</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,7 +1626,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1631,12 +1636,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,48 +1663,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128536490</v>
+        <v>128536758</v>
       </c>
       <c r="B11" t="n">
-        <v>80188</v>
+        <v>92742</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Högflon, Högflon, Jmt</t>
+          <t>Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447202</v>
+        <v>446993</v>
       </c>
       <c r="R11" t="n">
-        <v>6948032</v>
+        <v>6947982</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1758,12 +1758,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2004,45 +2004,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128536022</v>
+        <v>128534949</v>
       </c>
       <c r="B14" t="n">
-        <v>92742</v>
+        <v>57685</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447032</v>
+        <v>446459</v>
       </c>
       <c r="R14" t="n">
-        <v>6948185</v>
+        <v>6948172</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2074,7 +2079,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2084,7 +2089,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2111,50 +2121,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128534949</v>
+        <v>128536022</v>
       </c>
       <c r="B15" t="n">
-        <v>57685</v>
+        <v>92742</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446459</v>
+        <v>447032</v>
       </c>
       <c r="R15" t="n">
-        <v>6948172</v>
+        <v>6948185</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,7 +2191,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2196,12 +2201,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 16246-2024 artfynd.xlsx
+++ b/artfynd/A 16246-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128535830</v>
       </c>
       <c r="B2" t="n">
-        <v>92736</v>
+        <v>92742</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128536458</v>
       </c>
       <c r="B3" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128534788</v>
       </c>
       <c r="B4" t="n">
-        <v>92754</v>
+        <v>92760</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128537013</v>
       </c>
       <c r="B5" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>128536951</v>
       </c>
       <c r="B6" t="n">
-        <v>92754</v>
+        <v>92760</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128535657</v>
+        <v>128536962</v>
       </c>
       <c r="B7" t="n">
-        <v>57685</v>
+        <v>78844</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,39 +1226,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446810</v>
+        <v>446532</v>
       </c>
       <c r="R7" t="n">
-        <v>6948241</v>
+        <v>6948261</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,12 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128536962</v>
+        <v>128535657</v>
       </c>
       <c r="B8" t="n">
-        <v>78840</v>
+        <v>57689</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1343,34 +1333,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446532</v>
+        <v>446810</v>
       </c>
       <c r="R8" t="n">
-        <v>6948261</v>
+        <v>6948241</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1412,7 +1407,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,53 +1439,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128535023</v>
+        <v>128536758</v>
       </c>
       <c r="B9" t="n">
-        <v>57685</v>
+        <v>92748</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Högflon, Högflon, Jmt</t>
+          <t>Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446481</v>
+        <v>446993</v>
       </c>
       <c r="R9" t="n">
-        <v>6948165</v>
+        <v>6947982</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1514,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1524,12 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,12 +1534,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1559,7 +1549,7 @@
         <v>128536490</v>
       </c>
       <c r="B10" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,48 +1653,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128536758</v>
+        <v>128535023</v>
       </c>
       <c r="B11" t="n">
-        <v>92742</v>
+        <v>57689</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Högflon, Jmt</t>
+          <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446993</v>
+        <v>446481</v>
       </c>
       <c r="R11" t="n">
-        <v>6947982</v>
+        <v>6948165</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1733,7 +1728,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1743,7 +1738,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1758,12 +1758,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1773,7 +1773,7 @@
         <v>128535870</v>
       </c>
       <c r="B12" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>128534842</v>
       </c>
       <c r="B13" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128534949</v>
+        <v>128535281</v>
       </c>
       <c r="B14" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446459</v>
+        <v>446670</v>
       </c>
       <c r="R14" t="n">
-        <v>6948172</v>
+        <v>6948128</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2121,45 +2121,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128536022</v>
+        <v>128534949</v>
       </c>
       <c r="B15" t="n">
-        <v>92742</v>
+        <v>57689</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447032</v>
+        <v>446459</v>
       </c>
       <c r="R15" t="n">
-        <v>6948185</v>
+        <v>6948172</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2191,7 +2196,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2201,7 +2206,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2228,50 +2238,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128535281</v>
+        <v>128536022</v>
       </c>
       <c r="B16" t="n">
-        <v>57685</v>
+        <v>92748</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446670</v>
+        <v>447032</v>
       </c>
       <c r="R16" t="n">
-        <v>6948128</v>
+        <v>6948185</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2303,7 +2308,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2313,12 +2318,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2345,10 +2345,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128536769</v>
+        <v>128536398</v>
       </c>
       <c r="B17" t="n">
-        <v>80217</v>
+        <v>92748</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2356,21 +2356,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446993</v>
+        <v>447199</v>
       </c>
       <c r="R17" t="n">
-        <v>6948000</v>
+        <v>6948067</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128535194</v>
+        <v>128535206</v>
       </c>
       <c r="B18" t="n">
-        <v>78840</v>
+        <v>92742</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2463,21 +2463,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2493,7 +2493,7 @@
         <v>6948226</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2559,10 +2559,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128536398</v>
+        <v>128536769</v>
       </c>
       <c r="B19" t="n">
-        <v>92742</v>
+        <v>80221</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2570,21 +2570,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2594,10 +2594,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447199</v>
+        <v>446993</v>
       </c>
       <c r="R19" t="n">
-        <v>6948067</v>
+        <v>6948000</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2666,10 +2666,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128535206</v>
+        <v>128535194</v>
       </c>
       <c r="B20" t="n">
-        <v>92736</v>
+        <v>78844</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2677,21 +2677,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2707,7 +2707,7 @@
         <v>6948226</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2773,10 +2773,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128536454</v>
+        <v>128534979</v>
       </c>
       <c r="B21" t="n">
-        <v>80188</v>
+        <v>78844</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2784,21 +2784,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447211</v>
+        <v>446445</v>
       </c>
       <c r="R21" t="n">
-        <v>6948028</v>
+        <v>6948176</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2868,22 +2868,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128534979</v>
+        <v>128536454</v>
       </c>
       <c r="B22" t="n">
-        <v>78840</v>
+        <v>80192</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2891,21 +2891,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446445</v>
+        <v>447211</v>
       </c>
       <c r="R22" t="n">
-        <v>6948176</v>
+        <v>6948028</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2975,12 +2975,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2990,7 +2990,7 @@
         <v>128534878</v>
       </c>
       <c r="B23" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>128536515</v>
       </c>
       <c r="B24" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>128535763</v>
       </c>
       <c r="B25" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>128534677</v>
       </c>
       <c r="B26" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>128537036</v>
       </c>
       <c r="B27" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>128536136</v>
       </c>
       <c r="B28" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>128535656</v>
       </c>
       <c r="B29" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3795,32 +3795,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128536760</v>
+        <v>128535425</v>
       </c>
       <c r="B30" t="n">
-        <v>80188</v>
+        <v>92760</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446997</v>
+        <v>446718</v>
       </c>
       <c r="R30" t="n">
-        <v>6947997</v>
+        <v>6948094</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3902,32 +3902,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128535425</v>
+        <v>128536760</v>
       </c>
       <c r="B31" t="n">
-        <v>92754</v>
+        <v>80192</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4366</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446718</v>
+        <v>446997</v>
       </c>
       <c r="R31" t="n">
-        <v>6948094</v>
+        <v>6947997</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 16246-2024 artfynd.xlsx
+++ b/artfynd/A 16246-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128535830</v>
       </c>
       <c r="B2" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128536458</v>
       </c>
       <c r="B3" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128534788</v>
       </c>
       <c r="B4" t="n">
-        <v>92760</v>
+        <v>92766</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>128536951</v>
       </c>
       <c r="B6" t="n">
-        <v>92760</v>
+        <v>92766</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1439,48 +1439,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128536758</v>
+        <v>128536490</v>
       </c>
       <c r="B9" t="n">
-        <v>92748</v>
+        <v>80192</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Högflon, Jmt</t>
+          <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446993</v>
+        <v>447202</v>
       </c>
       <c r="R9" t="n">
-        <v>6947982</v>
+        <v>6948032</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,22 +1534,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128536490</v>
+        <v>128535023</v>
       </c>
       <c r="B10" t="n">
-        <v>80192</v>
+        <v>57689</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,34 +1557,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447202</v>
+        <v>446481</v>
       </c>
       <c r="R10" t="n">
-        <v>6948032</v>
+        <v>6948165</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1621,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1631,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,53 +1663,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128535023</v>
+        <v>128536758</v>
       </c>
       <c r="B11" t="n">
-        <v>57689</v>
+        <v>92754</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Högflon, Högflon, Jmt</t>
+          <t>Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446481</v>
+        <v>446993</v>
       </c>
       <c r="R11" t="n">
-        <v>6948165</v>
+        <v>6947982</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1728,7 +1733,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1738,12 +1743,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1758,12 +1758,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2004,7 +2004,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128535281</v>
+        <v>128534949</v>
       </c>
       <c r="B14" t="n">
         <v>57689</v>
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446670</v>
+        <v>446459</v>
       </c>
       <c r="R14" t="n">
-        <v>6948128</v>
+        <v>6948172</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2121,7 +2121,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128534949</v>
+        <v>128535281</v>
       </c>
       <c r="B15" t="n">
         <v>57689</v>
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446459</v>
+        <v>446670</v>
       </c>
       <c r="R15" t="n">
-        <v>6948172</v>
+        <v>6948128</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2241,7 +2241,7 @@
         <v>128536022</v>
       </c>
       <c r="B16" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2345,32 +2345,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128536398</v>
+        <v>128535194</v>
       </c>
       <c r="B17" t="n">
-        <v>92748</v>
+        <v>78844</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2380,13 +2380,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447199</v>
+        <v>446523</v>
       </c>
       <c r="R17" t="n">
-        <v>6948067</v>
+        <v>6948226</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2440,44 +2440,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128535206</v>
+        <v>128536769</v>
       </c>
       <c r="B18" t="n">
-        <v>92742</v>
+        <v>80221</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4362</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2487,13 +2487,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446523</v>
+        <v>446993</v>
       </c>
       <c r="R18" t="n">
-        <v>6948226</v>
+        <v>6948000</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2547,44 +2547,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128536769</v>
+        <v>128535206</v>
       </c>
       <c r="B19" t="n">
-        <v>80221</v>
+        <v>92748</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>4362</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2594,13 +2594,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446993</v>
+        <v>446523</v>
       </c>
       <c r="R19" t="n">
-        <v>6948000</v>
+        <v>6948226</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2654,44 +2654,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128535194</v>
+        <v>128536398</v>
       </c>
       <c r="B20" t="n">
-        <v>78844</v>
+        <v>92754</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2701,13 +2701,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446523</v>
+        <v>447199</v>
       </c>
       <c r="R20" t="n">
-        <v>6948226</v>
+        <v>6948067</v>
       </c>
       <c r="S20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2761,22 +2761,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128534979</v>
+        <v>128536454</v>
       </c>
       <c r="B21" t="n">
-        <v>78844</v>
+        <v>80192</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2784,21 +2784,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446445</v>
+        <v>447211</v>
       </c>
       <c r="R21" t="n">
-        <v>6948176</v>
+        <v>6948028</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2868,22 +2868,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128536454</v>
+        <v>128534979</v>
       </c>
       <c r="B22" t="n">
-        <v>80192</v>
+        <v>78844</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2891,21 +2891,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447211</v>
+        <v>446445</v>
       </c>
       <c r="R22" t="n">
-        <v>6948028</v>
+        <v>6948176</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2975,12 +2975,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3795,32 +3795,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128535425</v>
+        <v>128536760</v>
       </c>
       <c r="B30" t="n">
-        <v>92760</v>
+        <v>80192</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4366</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446718</v>
+        <v>446997</v>
       </c>
       <c r="R30" t="n">
-        <v>6948094</v>
+        <v>6947997</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3902,32 +3902,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128536760</v>
+        <v>128535425</v>
       </c>
       <c r="B31" t="n">
-        <v>80192</v>
+        <v>92766</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446997</v>
+        <v>446718</v>
       </c>
       <c r="R31" t="n">
-        <v>6947997</v>
+        <v>6948094</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 16246-2024 artfynd.xlsx
+++ b/artfynd/A 16246-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128535830</v>
       </c>
       <c r="B2" t="n">
-        <v>92748</v>
+        <v>92750</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128536458</v>
       </c>
       <c r="B3" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128534788</v>
       </c>
       <c r="B4" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>128536951</v>
       </c>
       <c r="B6" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128536962</v>
       </c>
       <c r="B7" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>128536490</v>
       </c>
       <c r="B9" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128536758</v>
       </c>
       <c r="B11" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2004,50 +2004,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128534949</v>
+        <v>128536022</v>
       </c>
       <c r="B14" t="n">
-        <v>57689</v>
+        <v>92756</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446459</v>
+        <v>447032</v>
       </c>
       <c r="R14" t="n">
-        <v>6948172</v>
+        <v>6948185</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,7 +2074,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2089,12 +2084,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2121,7 +2111,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128535281</v>
+        <v>128534949</v>
       </c>
       <c r="B15" t="n">
         <v>57689</v>
@@ -2161,10 +2151,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446670</v>
+        <v>446459</v>
       </c>
       <c r="R15" t="n">
-        <v>6948128</v>
+        <v>6948172</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2196,7 +2186,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2206,7 +2196,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2238,45 +2228,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128536022</v>
+        <v>128535281</v>
       </c>
       <c r="B16" t="n">
-        <v>92754</v>
+        <v>57689</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447032</v>
+        <v>446670</v>
       </c>
       <c r="R16" t="n">
-        <v>6948185</v>
+        <v>6948128</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2308,7 +2303,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2318,7 +2313,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2345,32 +2345,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128535194</v>
+        <v>128536769</v>
       </c>
       <c r="B17" t="n">
-        <v>78844</v>
+        <v>80223</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2380,13 +2380,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446523</v>
+        <v>446993</v>
       </c>
       <c r="R17" t="n">
-        <v>6948226</v>
+        <v>6948000</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2440,22 +2440,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128536769</v>
+        <v>128536398</v>
       </c>
       <c r="B18" t="n">
-        <v>80221</v>
+        <v>92756</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2463,21 +2463,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446993</v>
+        <v>447199</v>
       </c>
       <c r="R18" t="n">
-        <v>6948000</v>
+        <v>6948067</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2562,7 +2562,7 @@
         <v>128535206</v>
       </c>
       <c r="B19" t="n">
-        <v>92748</v>
+        <v>92750</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2666,32 +2666,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128536398</v>
+        <v>128535194</v>
       </c>
       <c r="B20" t="n">
-        <v>92754</v>
+        <v>78846</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2701,13 +2701,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447199</v>
+        <v>446523</v>
       </c>
       <c r="R20" t="n">
-        <v>6948067</v>
+        <v>6948226</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2761,12 +2761,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2776,7 +2776,7 @@
         <v>128536454</v>
       </c>
       <c r="B21" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>128534979</v>
       </c>
       <c r="B22" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>128537036</v>
       </c>
       <c r="B27" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3795,32 +3795,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128536760</v>
+        <v>128535425</v>
       </c>
       <c r="B30" t="n">
-        <v>80192</v>
+        <v>92768</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446997</v>
+        <v>446718</v>
       </c>
       <c r="R30" t="n">
-        <v>6947997</v>
+        <v>6948094</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3902,32 +3902,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128535425</v>
+        <v>128536760</v>
       </c>
       <c r="B31" t="n">
-        <v>92766</v>
+        <v>80194</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4366</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446718</v>
+        <v>446997</v>
       </c>
       <c r="R31" t="n">
-        <v>6948094</v>
+        <v>6947997</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 16246-2024 artfynd.xlsx
+++ b/artfynd/A 16246-2024 artfynd.xlsx
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128536962</v>
+        <v>128535657</v>
       </c>
       <c r="B7" t="n">
-        <v>78846</v>
+        <v>57689</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,34 +1226,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446532</v>
+        <v>446810</v>
       </c>
       <c r="R7" t="n">
-        <v>6948261</v>
+        <v>6948241</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1300,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128535657</v>
+        <v>128536962</v>
       </c>
       <c r="B8" t="n">
-        <v>57689</v>
+        <v>78846</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,39 +1343,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446810</v>
+        <v>446532</v>
       </c>
       <c r="R8" t="n">
-        <v>6948241</v>
+        <v>6948261</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,12 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1546,53 +1546,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128535023</v>
+        <v>128536758</v>
       </c>
       <c r="B10" t="n">
-        <v>57689</v>
+        <v>92756</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Högflon, Högflon, Jmt</t>
+          <t>Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446481</v>
+        <v>446993</v>
       </c>
       <c r="R10" t="n">
-        <v>6948165</v>
+        <v>6947982</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1621,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1631,12 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,60 +1641,65 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128536758</v>
+        <v>128535023</v>
       </c>
       <c r="B11" t="n">
-        <v>92756</v>
+        <v>57689</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Högflon, Jmt</t>
+          <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446993</v>
+        <v>446481</v>
       </c>
       <c r="R11" t="n">
-        <v>6947982</v>
+        <v>6948165</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1733,7 +1728,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1743,7 +1738,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1758,12 +1758,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2345,10 +2345,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128536769</v>
+        <v>128536398</v>
       </c>
       <c r="B17" t="n">
-        <v>80223</v>
+        <v>92756</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2356,21 +2356,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446993</v>
+        <v>447199</v>
       </c>
       <c r="R17" t="n">
-        <v>6948000</v>
+        <v>6948067</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2452,32 +2452,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128536398</v>
+        <v>128535206</v>
       </c>
       <c r="B18" t="n">
-        <v>92756</v>
+        <v>92750</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2487,13 +2487,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447199</v>
+        <v>446523</v>
       </c>
       <c r="R18" t="n">
-        <v>6948067</v>
+        <v>6948226</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2547,44 +2547,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128535206</v>
+        <v>128536769</v>
       </c>
       <c r="B19" t="n">
-        <v>92750</v>
+        <v>80223</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4362</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2594,13 +2594,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446523</v>
+        <v>446993</v>
       </c>
       <c r="R19" t="n">
-        <v>6948226</v>
+        <v>6948000</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2654,12 +2654,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128536454</v>
+        <v>128534979</v>
       </c>
       <c r="B21" t="n">
-        <v>80194</v>
+        <v>78846</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2784,21 +2784,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447211</v>
+        <v>446445</v>
       </c>
       <c r="R21" t="n">
-        <v>6948028</v>
+        <v>6948176</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2868,22 +2868,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128534979</v>
+        <v>128536454</v>
       </c>
       <c r="B22" t="n">
-        <v>78846</v>
+        <v>80194</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2891,21 +2891,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446445</v>
+        <v>447211</v>
       </c>
       <c r="R22" t="n">
-        <v>6948176</v>
+        <v>6948028</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2975,12 +2975,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3795,32 +3795,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128535425</v>
+        <v>128536760</v>
       </c>
       <c r="B30" t="n">
-        <v>92768</v>
+        <v>80194</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4366</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446718</v>
+        <v>446997</v>
       </c>
       <c r="R30" t="n">
-        <v>6948094</v>
+        <v>6947997</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3902,32 +3902,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128536760</v>
+        <v>128535425</v>
       </c>
       <c r="B31" t="n">
-        <v>80194</v>
+        <v>92768</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446997</v>
+        <v>446718</v>
       </c>
       <c r="R31" t="n">
-        <v>6947997</v>
+        <v>6948094</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 16246-2024 artfynd.xlsx
+++ b/artfynd/A 16246-2024 artfynd.xlsx
@@ -1439,48 +1439,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128536490</v>
+        <v>128536758</v>
       </c>
       <c r="B9" t="n">
-        <v>80194</v>
+        <v>92756</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Högflon, Högflon, Jmt</t>
+          <t>Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447202</v>
+        <v>446993</v>
       </c>
       <c r="R9" t="n">
-        <v>6948032</v>
+        <v>6947982</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,60 +1534,65 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128536758</v>
+        <v>128535023</v>
       </c>
       <c r="B10" t="n">
-        <v>92756</v>
+        <v>57689</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Högflon, Jmt</t>
+          <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446993</v>
+        <v>446481</v>
       </c>
       <c r="R10" t="n">
-        <v>6947982</v>
+        <v>6948165</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1616,7 +1621,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1631,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,22 +1651,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128535023</v>
+        <v>128536490</v>
       </c>
       <c r="B11" t="n">
-        <v>57689</v>
+        <v>80194</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,39 +1674,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446481</v>
+        <v>447202</v>
       </c>
       <c r="R11" t="n">
-        <v>6948165</v>
+        <v>6948032</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,7 +1733,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1738,12 +1743,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 16246-2024 artfynd.xlsx
+++ b/artfynd/A 16246-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128535830</v>
       </c>
       <c r="B2" t="n">
-        <v>92750</v>
+        <v>92751</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128536458</v>
       </c>
       <c r="B3" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128534788</v>
       </c>
       <c r="B4" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>128536951</v>
       </c>
       <c r="B6" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128535657</v>
+        <v>128536962</v>
       </c>
       <c r="B7" t="n">
-        <v>57689</v>
+        <v>78846</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,39 +1226,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446810</v>
+        <v>446532</v>
       </c>
       <c r="R7" t="n">
-        <v>6948241</v>
+        <v>6948261</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,12 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128536962</v>
+        <v>128535657</v>
       </c>
       <c r="B8" t="n">
-        <v>78846</v>
+        <v>57689</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1343,34 +1333,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446532</v>
+        <v>446810</v>
       </c>
       <c r="R8" t="n">
-        <v>6948261</v>
+        <v>6948241</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1412,7 +1407,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,48 +1439,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128536758</v>
+        <v>128536490</v>
       </c>
       <c r="B9" t="n">
-        <v>92756</v>
+        <v>80194</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Högflon, Jmt</t>
+          <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446993</v>
+        <v>447202</v>
       </c>
       <c r="R9" t="n">
-        <v>6947982</v>
+        <v>6948032</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,65 +1534,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128535023</v>
+        <v>128536758</v>
       </c>
       <c r="B10" t="n">
-        <v>57689</v>
+        <v>92757</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Högflon, Högflon, Jmt</t>
+          <t>Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446481</v>
+        <v>446993</v>
       </c>
       <c r="R10" t="n">
-        <v>6948165</v>
+        <v>6947982</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1621,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1631,12 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,22 +1641,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128536490</v>
+        <v>128535023</v>
       </c>
       <c r="B11" t="n">
-        <v>80194</v>
+        <v>57689</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,34 +1664,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447202</v>
+        <v>446481</v>
       </c>
       <c r="R11" t="n">
-        <v>6948032</v>
+        <v>6948165</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,7 +1728,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1743,7 +1738,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2007,7 +2007,7 @@
         <v>128536022</v>
       </c>
       <c r="B14" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128534949</v>
+        <v>128535281</v>
       </c>
       <c r="B15" t="n">
         <v>57689</v>
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446459</v>
+        <v>446670</v>
       </c>
       <c r="R15" t="n">
-        <v>6948172</v>
+        <v>6948128</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2228,7 +2228,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128535281</v>
+        <v>128534949</v>
       </c>
       <c r="B16" t="n">
         <v>57689</v>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446670</v>
+        <v>446459</v>
       </c>
       <c r="R16" t="n">
-        <v>6948128</v>
+        <v>6948172</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2345,32 +2345,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128536398</v>
+        <v>128535206</v>
       </c>
       <c r="B17" t="n">
-        <v>92756</v>
+        <v>92751</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2380,13 +2380,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447199</v>
+        <v>446523</v>
       </c>
       <c r="R17" t="n">
-        <v>6948067</v>
+        <v>6948226</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2440,44 +2440,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128535206</v>
+        <v>128536769</v>
       </c>
       <c r="B18" t="n">
-        <v>92750</v>
+        <v>80223</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4362</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2487,13 +2487,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446523</v>
+        <v>446993</v>
       </c>
       <c r="R18" t="n">
-        <v>6948226</v>
+        <v>6948000</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2547,44 +2547,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128536769</v>
+        <v>128535194</v>
       </c>
       <c r="B19" t="n">
-        <v>80223</v>
+        <v>78846</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2594,13 +2594,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446993</v>
+        <v>446523</v>
       </c>
       <c r="R19" t="n">
-        <v>6948000</v>
+        <v>6948226</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2654,44 +2654,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128535194</v>
+        <v>128536398</v>
       </c>
       <c r="B20" t="n">
-        <v>78846</v>
+        <v>92757</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2701,13 +2701,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446523</v>
+        <v>447199</v>
       </c>
       <c r="R20" t="n">
-        <v>6948226</v>
+        <v>6948067</v>
       </c>
       <c r="S20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2761,12 +2761,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3795,32 +3795,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128536760</v>
+        <v>128535425</v>
       </c>
       <c r="B30" t="n">
-        <v>80194</v>
+        <v>92769</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446997</v>
+        <v>446718</v>
       </c>
       <c r="R30" t="n">
-        <v>6947997</v>
+        <v>6948094</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3902,32 +3902,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128535425</v>
+        <v>128536760</v>
       </c>
       <c r="B31" t="n">
-        <v>92768</v>
+        <v>80194</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4366</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446718</v>
+        <v>446997</v>
       </c>
       <c r="R31" t="n">
-        <v>6948094</v>
+        <v>6947997</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 16246-2024 artfynd.xlsx
+++ b/artfynd/A 16246-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128535830</v>
       </c>
       <c r="B2" t="n">
-        <v>92751</v>
+        <v>92778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128536458</v>
       </c>
       <c r="B3" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128534788</v>
       </c>
       <c r="B4" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128537013</v>
       </c>
       <c r="B5" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>128536951</v>
       </c>
       <c r="B6" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128536962</v>
       </c>
       <c r="B7" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>128535657</v>
       </c>
       <c r="B8" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,48 +1439,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128536490</v>
+        <v>128536758</v>
       </c>
       <c r="B9" t="n">
-        <v>80194</v>
+        <v>92784</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Högflon, Högflon, Jmt</t>
+          <t>Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447202</v>
+        <v>446993</v>
       </c>
       <c r="R9" t="n">
-        <v>6948032</v>
+        <v>6947982</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,60 +1534,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128536758</v>
+        <v>128536490</v>
       </c>
       <c r="B10" t="n">
-        <v>92757</v>
+        <v>80221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Högflon, Jmt</t>
+          <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446993</v>
+        <v>447202</v>
       </c>
       <c r="R10" t="n">
-        <v>6947982</v>
+        <v>6948032</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,12 +1641,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1656,7 +1656,7 @@
         <v>128535023</v>
       </c>
       <c r="B11" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128535870</v>
       </c>
       <c r="B12" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>128534842</v>
       </c>
       <c r="B13" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2004,45 +2004,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128536022</v>
+        <v>128535281</v>
       </c>
       <c r="B14" t="n">
-        <v>92757</v>
+        <v>57716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447032</v>
+        <v>446670</v>
       </c>
       <c r="R14" t="n">
-        <v>6948185</v>
+        <v>6948128</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2074,7 +2079,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2084,7 +2089,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2111,10 +2121,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128535281</v>
+        <v>128534949</v>
       </c>
       <c r="B15" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,10 +2161,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446670</v>
+        <v>446459</v>
       </c>
       <c r="R15" t="n">
-        <v>6948128</v>
+        <v>6948172</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,7 +2196,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2196,7 +2206,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2228,50 +2238,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128534949</v>
+        <v>128536022</v>
       </c>
       <c r="B16" t="n">
-        <v>57689</v>
+        <v>92784</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446459</v>
+        <v>447032</v>
       </c>
       <c r="R16" t="n">
-        <v>6948172</v>
+        <v>6948185</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2303,7 +2308,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2313,12 +2318,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2348,7 +2348,7 @@
         <v>128535206</v>
       </c>
       <c r="B17" t="n">
-        <v>92751</v>
+        <v>92778</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128536769</v>
+        <v>128536398</v>
       </c>
       <c r="B18" t="n">
-        <v>80223</v>
+        <v>92784</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2463,21 +2463,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446993</v>
+        <v>447199</v>
       </c>
       <c r="R18" t="n">
-        <v>6948000</v>
+        <v>6948067</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2559,32 +2559,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128535194</v>
+        <v>128536769</v>
       </c>
       <c r="B19" t="n">
-        <v>78846</v>
+        <v>80250</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2594,13 +2594,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446523</v>
+        <v>446993</v>
       </c>
       <c r="R19" t="n">
-        <v>6948226</v>
+        <v>6948000</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2654,44 +2654,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128536398</v>
+        <v>128535194</v>
       </c>
       <c r="B20" t="n">
-        <v>92757</v>
+        <v>78873</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2701,13 +2701,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447199</v>
+        <v>446523</v>
       </c>
       <c r="R20" t="n">
-        <v>6948067</v>
+        <v>6948226</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2761,12 +2761,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2776,7 +2776,7 @@
         <v>128534979</v>
       </c>
       <c r="B21" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>128536454</v>
       </c>
       <c r="B22" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>128534878</v>
       </c>
       <c r="B23" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>128536515</v>
       </c>
       <c r="B24" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>128535763</v>
       </c>
       <c r="B25" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>128534677</v>
       </c>
       <c r="B26" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>128537036</v>
       </c>
       <c r="B27" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>128536136</v>
       </c>
       <c r="B28" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>128535656</v>
       </c>
       <c r="B29" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>128535425</v>
       </c>
       <c r="B30" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>128536760</v>
       </c>
       <c r="B31" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 16246-2024 artfynd.xlsx
+++ b/artfynd/A 16246-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128535830</v>
       </c>
       <c r="B2" t="n">
-        <v>92778</v>
+        <v>92783</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128536458</v>
       </c>
       <c r="B3" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128534788</v>
       </c>
       <c r="B4" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>128536951</v>
       </c>
       <c r="B6" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128536962</v>
       </c>
       <c r="B7" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1439,48 +1439,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128536758</v>
+        <v>128536490</v>
       </c>
       <c r="B9" t="n">
-        <v>92784</v>
+        <v>80225</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Högflon, Jmt</t>
+          <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446993</v>
+        <v>447202</v>
       </c>
       <c r="R9" t="n">
-        <v>6947982</v>
+        <v>6948032</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,60 +1534,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128536490</v>
+        <v>128536758</v>
       </c>
       <c r="B10" t="n">
-        <v>80221</v>
+        <v>92789</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Högflon, Högflon, Jmt</t>
+          <t>Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447202</v>
+        <v>446993</v>
       </c>
       <c r="R10" t="n">
-        <v>6948032</v>
+        <v>6947982</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,12 +1641,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2004,50 +2004,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128535281</v>
+        <v>128536022</v>
       </c>
       <c r="B14" t="n">
-        <v>57716</v>
+        <v>92789</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446670</v>
+        <v>447032</v>
       </c>
       <c r="R14" t="n">
-        <v>6948128</v>
+        <v>6948185</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,7 +2074,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2089,12 +2084,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2121,7 +2111,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128534949</v>
+        <v>128535281</v>
       </c>
       <c r="B15" t="n">
         <v>57716</v>
@@ -2161,10 +2151,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446459</v>
+        <v>446670</v>
       </c>
       <c r="R15" t="n">
-        <v>6948172</v>
+        <v>6948128</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2196,7 +2186,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2206,7 +2196,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2238,45 +2228,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128536022</v>
+        <v>128534949</v>
       </c>
       <c r="B16" t="n">
-        <v>92784</v>
+        <v>57716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447032</v>
+        <v>446459</v>
       </c>
       <c r="R16" t="n">
-        <v>6948185</v>
+        <v>6948172</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2308,7 +2303,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2318,7 +2313,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2345,32 +2345,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128535206</v>
+        <v>128536769</v>
       </c>
       <c r="B17" t="n">
-        <v>92778</v>
+        <v>80254</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4362</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2380,13 +2380,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446523</v>
+        <v>446993</v>
       </c>
       <c r="R17" t="n">
-        <v>6948226</v>
+        <v>6948000</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2440,44 +2440,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128536398</v>
+        <v>128535194</v>
       </c>
       <c r="B18" t="n">
-        <v>92784</v>
+        <v>78877</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2487,13 +2487,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447199</v>
+        <v>446523</v>
       </c>
       <c r="R18" t="n">
-        <v>6948067</v>
+        <v>6948226</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2547,44 +2547,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128536769</v>
+        <v>128535206</v>
       </c>
       <c r="B19" t="n">
-        <v>80250</v>
+        <v>92783</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>4362</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2594,13 +2594,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446993</v>
+        <v>446523</v>
       </c>
       <c r="R19" t="n">
-        <v>6948000</v>
+        <v>6948226</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2654,44 +2654,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128535194</v>
+        <v>128536398</v>
       </c>
       <c r="B20" t="n">
-        <v>78873</v>
+        <v>92789</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2701,13 +2701,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446523</v>
+        <v>447199</v>
       </c>
       <c r="R20" t="n">
-        <v>6948226</v>
+        <v>6948067</v>
       </c>
       <c r="S20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2761,12 +2761,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2776,7 +2776,7 @@
         <v>128534979</v>
       </c>
       <c r="B21" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>128536454</v>
       </c>
       <c r="B22" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>128537036</v>
       </c>
       <c r="B27" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3795,32 +3795,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128535425</v>
+        <v>128536760</v>
       </c>
       <c r="B30" t="n">
-        <v>92796</v>
+        <v>80225</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4366</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446718</v>
+        <v>446997</v>
       </c>
       <c r="R30" t="n">
-        <v>6948094</v>
+        <v>6947997</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3902,32 +3902,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128536760</v>
+        <v>128535425</v>
       </c>
       <c r="B31" t="n">
-        <v>80221</v>
+        <v>92801</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446997</v>
+        <v>446718</v>
       </c>
       <c r="R31" t="n">
-        <v>6947997</v>
+        <v>6948094</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 16246-2024 artfynd.xlsx
+++ b/artfynd/A 16246-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128535830</v>
       </c>
       <c r="B2" t="n">
-        <v>92783</v>
+        <v>92788</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128536458</v>
       </c>
       <c r="B3" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,48 +889,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128534788</v>
+        <v>128537013</v>
       </c>
       <c r="B4" t="n">
-        <v>92801</v>
+        <v>57876</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446383</v>
+        <v>446498</v>
       </c>
       <c r="R4" t="n">
-        <v>6948178</v>
+        <v>6948254</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,65 +989,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128537013</v>
+        <v>128534788</v>
       </c>
       <c r="B5" t="n">
-        <v>57876</v>
+        <v>92806</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446498</v>
+        <v>446383</v>
       </c>
       <c r="R5" t="n">
-        <v>6948254</v>
+        <v>6948178</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,12 +1096,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1111,7 +1111,7 @@
         <v>128536951</v>
       </c>
       <c r="B6" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1439,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128536490</v>
+        <v>128535023</v>
       </c>
       <c r="B9" t="n">
-        <v>80225</v>
+        <v>57716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,34 +1450,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447202</v>
+        <v>446481</v>
       </c>
       <c r="R9" t="n">
-        <v>6948032</v>
+        <v>6948165</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,7 +1514,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1524,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,7 +1559,7 @@
         <v>128536758</v>
       </c>
       <c r="B10" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1653,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128535023</v>
+        <v>128536490</v>
       </c>
       <c r="B11" t="n">
-        <v>57716</v>
+        <v>80225</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,39 +1674,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446481</v>
+        <v>447202</v>
       </c>
       <c r="R11" t="n">
-        <v>6948165</v>
+        <v>6948032</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,7 +1733,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1738,12 +1743,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2007,7 +2007,7 @@
         <v>128536022</v>
       </c>
       <c r="B14" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128535281</v>
+        <v>128534949</v>
       </c>
       <c r="B15" t="n">
         <v>57716</v>
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446670</v>
+        <v>446459</v>
       </c>
       <c r="R15" t="n">
-        <v>6948128</v>
+        <v>6948172</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2228,7 +2228,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128534949</v>
+        <v>128535281</v>
       </c>
       <c r="B16" t="n">
         <v>57716</v>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446459</v>
+        <v>446670</v>
       </c>
       <c r="R16" t="n">
-        <v>6948172</v>
+        <v>6948128</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2452,32 +2452,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128535194</v>
+        <v>128536398</v>
       </c>
       <c r="B18" t="n">
-        <v>78877</v>
+        <v>92794</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2487,13 +2487,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446523</v>
+        <v>447199</v>
       </c>
       <c r="R18" t="n">
-        <v>6948226</v>
+        <v>6948067</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2547,12 +2547,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2562,7 +2562,7 @@
         <v>128535206</v>
       </c>
       <c r="B19" t="n">
-        <v>92783</v>
+        <v>92788</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2666,32 +2666,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128536398</v>
+        <v>128535194</v>
       </c>
       <c r="B20" t="n">
-        <v>92789</v>
+        <v>78877</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2701,13 +2701,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447199</v>
+        <v>446523</v>
       </c>
       <c r="R20" t="n">
-        <v>6948067</v>
+        <v>6948226</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2761,22 +2761,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128534979</v>
+        <v>128536454</v>
       </c>
       <c r="B21" t="n">
-        <v>78877</v>
+        <v>80225</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2784,21 +2784,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446445</v>
+        <v>447211</v>
       </c>
       <c r="R21" t="n">
-        <v>6948176</v>
+        <v>6948028</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2868,22 +2868,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128536454</v>
+        <v>128534979</v>
       </c>
       <c r="B22" t="n">
-        <v>80225</v>
+        <v>78877</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2891,21 +2891,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447211</v>
+        <v>446445</v>
       </c>
       <c r="R22" t="n">
-        <v>6948028</v>
+        <v>6948176</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2975,12 +2975,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3905,7 +3905,7 @@
         <v>128535425</v>
       </c>
       <c r="B31" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 16246-2024 artfynd.xlsx
+++ b/artfynd/A 16246-2024 artfynd.xlsx
@@ -889,53 +889,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128537013</v>
+        <v>128534788</v>
       </c>
       <c r="B4" t="n">
-        <v>57876</v>
+        <v>92806</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446498</v>
+        <v>446383</v>
       </c>
       <c r="R4" t="n">
-        <v>6948254</v>
+        <v>6948178</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,60 +984,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128534788</v>
+        <v>128537013</v>
       </c>
       <c r="B5" t="n">
-        <v>92806</v>
+        <v>57876</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446383</v>
+        <v>446498</v>
       </c>
       <c r="R5" t="n">
-        <v>6948178</v>
+        <v>6948254</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,12 +1096,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1439,53 +1439,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128535023</v>
+        <v>128536758</v>
       </c>
       <c r="B9" t="n">
-        <v>57716</v>
+        <v>92794</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Högflon, Högflon, Jmt</t>
+          <t>Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446481</v>
+        <v>446993</v>
       </c>
       <c r="R9" t="n">
-        <v>6948165</v>
+        <v>6947982</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1514,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1524,12 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,60 +1534,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128536758</v>
+        <v>128536490</v>
       </c>
       <c r="B10" t="n">
-        <v>92794</v>
+        <v>80225</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Högflon, Jmt</t>
+          <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446993</v>
+        <v>447202</v>
       </c>
       <c r="R10" t="n">
-        <v>6947982</v>
+        <v>6948032</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1626,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1636,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,22 +1641,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128536490</v>
+        <v>128535023</v>
       </c>
       <c r="B11" t="n">
-        <v>80225</v>
+        <v>57716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,34 +1664,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447202</v>
+        <v>446481</v>
       </c>
       <c r="R11" t="n">
-        <v>6948032</v>
+        <v>6948165</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,7 +1728,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1743,7 +1738,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2111,7 +2111,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128534949</v>
+        <v>128535281</v>
       </c>
       <c r="B15" t="n">
         <v>57716</v>
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446459</v>
+        <v>446670</v>
       </c>
       <c r="R15" t="n">
-        <v>6948172</v>
+        <v>6948128</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2228,7 +2228,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128535281</v>
+        <v>128534949</v>
       </c>
       <c r="B16" t="n">
         <v>57716</v>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446670</v>
+        <v>446459</v>
       </c>
       <c r="R16" t="n">
-        <v>6948128</v>
+        <v>6948172</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2452,32 +2452,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128536398</v>
+        <v>128535194</v>
       </c>
       <c r="B18" t="n">
-        <v>92794</v>
+        <v>78877</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2487,13 +2487,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447199</v>
+        <v>446523</v>
       </c>
       <c r="R18" t="n">
-        <v>6948067</v>
+        <v>6948226</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2547,44 +2547,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128535206</v>
+        <v>128536398</v>
       </c>
       <c r="B19" t="n">
-        <v>92788</v>
+        <v>92794</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2594,13 +2594,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446523</v>
+        <v>447199</v>
       </c>
       <c r="R19" t="n">
-        <v>6948226</v>
+        <v>6948067</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2654,22 +2654,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128535194</v>
+        <v>128535206</v>
       </c>
       <c r="B20" t="n">
-        <v>78877</v>
+        <v>92788</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2677,21 +2677,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2707,7 +2707,7 @@
         <v>6948226</v>
       </c>
       <c r="S20" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2773,10 +2773,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128536454</v>
+        <v>128534979</v>
       </c>
       <c r="B21" t="n">
-        <v>80225</v>
+        <v>78877</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2784,21 +2784,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447211</v>
+        <v>446445</v>
       </c>
       <c r="R21" t="n">
-        <v>6948028</v>
+        <v>6948176</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2868,22 +2868,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128534979</v>
+        <v>128536454</v>
       </c>
       <c r="B22" t="n">
-        <v>78877</v>
+        <v>80225</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2891,21 +2891,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446445</v>
+        <v>447211</v>
       </c>
       <c r="R22" t="n">
-        <v>6948176</v>
+        <v>6948028</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2975,12 +2975,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3795,32 +3795,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128536760</v>
+        <v>128535425</v>
       </c>
       <c r="B30" t="n">
-        <v>80225</v>
+        <v>92806</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446997</v>
+        <v>446718</v>
       </c>
       <c r="R30" t="n">
-        <v>6947997</v>
+        <v>6948094</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3902,32 +3902,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128535425</v>
+        <v>128536760</v>
       </c>
       <c r="B31" t="n">
-        <v>92806</v>
+        <v>80225</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4366</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446718</v>
+        <v>446997</v>
       </c>
       <c r="R31" t="n">
-        <v>6948094</v>
+        <v>6947997</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 16246-2024 artfynd.xlsx
+++ b/artfynd/A 16246-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128535830</v>
       </c>
       <c r="B2" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128536458</v>
       </c>
       <c r="B3" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128534788</v>
       </c>
       <c r="B4" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128537013</v>
       </c>
       <c r="B5" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>128536951</v>
       </c>
       <c r="B6" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128536962</v>
       </c>
       <c r="B7" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>128535657</v>
       </c>
       <c r="B8" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>128536758</v>
       </c>
       <c r="B9" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>128536490</v>
       </c>
       <c r="B10" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128535023</v>
       </c>
       <c r="B11" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128535870</v>
       </c>
       <c r="B12" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>128534842</v>
       </c>
       <c r="B13" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2004,45 +2004,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128536022</v>
+        <v>128535281</v>
       </c>
       <c r="B14" t="n">
-        <v>92794</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447032</v>
+        <v>446670</v>
       </c>
       <c r="R14" t="n">
-        <v>6948185</v>
+        <v>6948128</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2074,7 +2079,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2084,7 +2089,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2111,10 +2121,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128535281</v>
+        <v>128534949</v>
       </c>
       <c r="B15" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,10 +2161,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446670</v>
+        <v>446459</v>
       </c>
       <c r="R15" t="n">
-        <v>6948128</v>
+        <v>6948172</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,7 +2196,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2196,7 +2206,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2228,50 +2238,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128534949</v>
+        <v>128536022</v>
       </c>
       <c r="B16" t="n">
-        <v>57716</v>
+        <v>92798</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446459</v>
+        <v>447032</v>
       </c>
       <c r="R16" t="n">
-        <v>6948172</v>
+        <v>6948185</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2303,7 +2308,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2313,12 +2318,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2348,7 +2348,7 @@
         <v>128536769</v>
       </c>
       <c r="B17" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>128535194</v>
       </c>
       <c r="B18" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>128536398</v>
       </c>
       <c r="B19" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>128535206</v>
       </c>
       <c r="B20" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>128534979</v>
       </c>
       <c r="B21" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>128536454</v>
       </c>
       <c r="B22" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>128534878</v>
       </c>
       <c r="B23" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>128536515</v>
       </c>
       <c r="B24" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>128535763</v>
       </c>
       <c r="B25" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>128534677</v>
       </c>
       <c r="B26" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>128537036</v>
       </c>
       <c r="B27" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>128536136</v>
       </c>
       <c r="B28" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>128535656</v>
       </c>
       <c r="B29" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3795,32 +3795,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128535425</v>
+        <v>128536760</v>
       </c>
       <c r="B30" t="n">
-        <v>92806</v>
+        <v>80229</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4366</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446718</v>
+        <v>446997</v>
       </c>
       <c r="R30" t="n">
-        <v>6948094</v>
+        <v>6947997</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3902,32 +3902,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128536760</v>
+        <v>128535425</v>
       </c>
       <c r="B31" t="n">
-        <v>80225</v>
+        <v>92810</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446997</v>
+        <v>446718</v>
       </c>
       <c r="R31" t="n">
-        <v>6947997</v>
+        <v>6948094</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 16246-2024 artfynd.xlsx
+++ b/artfynd/A 16246-2024 artfynd.xlsx
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128536490</v>
+        <v>128535023</v>
       </c>
       <c r="B10" t="n">
-        <v>80229</v>
+        <v>57720</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,34 +1557,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447202</v>
+        <v>446481</v>
       </c>
       <c r="R10" t="n">
-        <v>6948032</v>
+        <v>6948165</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1621,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1631,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128535023</v>
+        <v>128536490</v>
       </c>
       <c r="B11" t="n">
-        <v>57720</v>
+        <v>80229</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,39 +1674,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446481</v>
+        <v>447202</v>
       </c>
       <c r="R11" t="n">
-        <v>6948165</v>
+        <v>6948032</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,7 +1733,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1738,12 +1743,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2004,50 +2004,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128535281</v>
+        <v>128536022</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>92798</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446670</v>
+        <v>447032</v>
       </c>
       <c r="R14" t="n">
-        <v>6948128</v>
+        <v>6948185</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,7 +2074,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2089,12 +2084,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2121,7 +2111,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128534949</v>
+        <v>128535281</v>
       </c>
       <c r="B15" t="n">
         <v>57720</v>
@@ -2161,10 +2151,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446459</v>
+        <v>446670</v>
       </c>
       <c r="R15" t="n">
-        <v>6948172</v>
+        <v>6948128</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2196,7 +2186,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2206,7 +2196,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2238,45 +2228,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128536022</v>
+        <v>128534949</v>
       </c>
       <c r="B16" t="n">
-        <v>92798</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447032</v>
+        <v>446459</v>
       </c>
       <c r="R16" t="n">
-        <v>6948185</v>
+        <v>6948172</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2308,7 +2303,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2318,7 +2313,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2345,32 +2345,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128536769</v>
+        <v>128535194</v>
       </c>
       <c r="B17" t="n">
-        <v>80258</v>
+        <v>78881</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2380,13 +2380,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446993</v>
+        <v>446523</v>
       </c>
       <c r="R17" t="n">
-        <v>6948000</v>
+        <v>6948226</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2440,44 +2440,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128535194</v>
+        <v>128536769</v>
       </c>
       <c r="B18" t="n">
-        <v>78881</v>
+        <v>80258</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2487,13 +2487,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446523</v>
+        <v>446993</v>
       </c>
       <c r="R18" t="n">
-        <v>6948226</v>
+        <v>6948000</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2547,12 +2547,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3795,32 +3795,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128536760</v>
+        <v>128535425</v>
       </c>
       <c r="B30" t="n">
-        <v>80229</v>
+        <v>92810</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446997</v>
+        <v>446718</v>
       </c>
       <c r="R30" t="n">
-        <v>6947997</v>
+        <v>6948094</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3902,32 +3902,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128535425</v>
+        <v>128536760</v>
       </c>
       <c r="B31" t="n">
-        <v>92810</v>
+        <v>80229</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4366</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446718</v>
+        <v>446997</v>
       </c>
       <c r="R31" t="n">
-        <v>6948094</v>
+        <v>6947997</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 16246-2024 artfynd.xlsx
+++ b/artfynd/A 16246-2024 artfynd.xlsx
@@ -1439,48 +1439,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128536758</v>
+        <v>128535023</v>
       </c>
       <c r="B9" t="n">
-        <v>92798</v>
+        <v>57720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Högflon, Jmt</t>
+          <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446993</v>
+        <v>446481</v>
       </c>
       <c r="R9" t="n">
-        <v>6947982</v>
+        <v>6948165</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,7 +1514,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1524,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,65 +1544,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128535023</v>
+        <v>128536758</v>
       </c>
       <c r="B10" t="n">
-        <v>57720</v>
+        <v>92798</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Högflon, Högflon, Jmt</t>
+          <t>Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446481</v>
+        <v>446993</v>
       </c>
       <c r="R10" t="n">
-        <v>6948165</v>
+        <v>6947982</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1621,7 +1626,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1631,12 +1636,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,12 +1651,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2345,32 +2345,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128535194</v>
+        <v>128536398</v>
       </c>
       <c r="B17" t="n">
-        <v>78881</v>
+        <v>92798</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2380,13 +2380,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446523</v>
+        <v>447199</v>
       </c>
       <c r="R17" t="n">
-        <v>6948226</v>
+        <v>6948067</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2440,44 +2440,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128536769</v>
+        <v>128535206</v>
       </c>
       <c r="B18" t="n">
-        <v>80258</v>
+        <v>92792</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>4362</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2487,13 +2487,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446993</v>
+        <v>446523</v>
       </c>
       <c r="R18" t="n">
-        <v>6948000</v>
+        <v>6948226</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2547,44 +2547,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128536398</v>
+        <v>128535194</v>
       </c>
       <c r="B19" t="n">
-        <v>92798</v>
+        <v>78881</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2594,13 +2594,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447199</v>
+        <v>446523</v>
       </c>
       <c r="R19" t="n">
-        <v>6948067</v>
+        <v>6948226</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2654,44 +2654,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128535206</v>
+        <v>128536769</v>
       </c>
       <c r="B20" t="n">
-        <v>92792</v>
+        <v>80258</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4362</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2701,13 +2701,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446523</v>
+        <v>446993</v>
       </c>
       <c r="R20" t="n">
-        <v>6948226</v>
+        <v>6948000</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2761,12 +2761,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 16246-2024 artfynd.xlsx
+++ b/artfynd/A 16246-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128535830</v>
       </c>
       <c r="B2" t="n">
-        <v>92792</v>
+        <v>92797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128536458</v>
       </c>
       <c r="B3" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128534788</v>
       </c>
       <c r="B4" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128537013</v>
       </c>
       <c r="B5" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>128536951</v>
       </c>
       <c r="B6" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128536962</v>
       </c>
       <c r="B7" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>128535657</v>
       </c>
       <c r="B8" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>128535023</v>
       </c>
       <c r="B9" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>128536758</v>
       </c>
       <c r="B10" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128536490</v>
       </c>
       <c r="B11" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128535870</v>
       </c>
       <c r="B12" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>128534842</v>
       </c>
       <c r="B13" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>128536022</v>
       </c>
       <c r="B14" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>128535281</v>
       </c>
       <c r="B15" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>128534949</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>128536398</v>
       </c>
       <c r="B17" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>128535206</v>
       </c>
       <c r="B18" t="n">
-        <v>92792</v>
+        <v>92797</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2559,32 +2559,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128535194</v>
+        <v>128536769</v>
       </c>
       <c r="B19" t="n">
-        <v>78881</v>
+        <v>80163</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2594,13 +2594,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446523</v>
+        <v>446993</v>
       </c>
       <c r="R19" t="n">
-        <v>6948226</v>
+        <v>6948000</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2654,44 +2654,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128536769</v>
+        <v>128535194</v>
       </c>
       <c r="B20" t="n">
-        <v>80258</v>
+        <v>78786</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2701,13 +2701,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446993</v>
+        <v>446523</v>
       </c>
       <c r="R20" t="n">
-        <v>6948000</v>
+        <v>6948226</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2761,12 +2761,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2776,7 +2776,7 @@
         <v>128534979</v>
       </c>
       <c r="B21" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>128536454</v>
       </c>
       <c r="B22" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>128534878</v>
       </c>
       <c r="B23" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3103,10 +3103,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128536515</v>
+        <v>128535763</v>
       </c>
       <c r="B24" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447214</v>
+        <v>446882</v>
       </c>
       <c r="R24" t="n">
-        <v>6948006</v>
+        <v>6948260</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3220,10 +3220,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128535763</v>
+        <v>128536515</v>
       </c>
       <c r="B25" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3260,10 +3260,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446882</v>
+        <v>447214</v>
       </c>
       <c r="R25" t="n">
-        <v>6948260</v>
+        <v>6948006</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3340,7 +3340,7 @@
         <v>128534677</v>
       </c>
       <c r="B26" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>128537036</v>
       </c>
       <c r="B27" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>128536136</v>
       </c>
       <c r="B28" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>128535656</v>
       </c>
       <c r="B29" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>128535425</v>
       </c>
       <c r="B30" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>128536760</v>
       </c>
       <c r="B31" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 16246-2024 artfynd.xlsx
+++ b/artfynd/A 16246-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128535830</v>
       </c>
       <c r="B2" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128536458</v>
       </c>
       <c r="B3" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128534788</v>
       </c>
       <c r="B4" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>128536951</v>
       </c>
       <c r="B6" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128536962</v>
       </c>
       <c r="B7" t="n">
-        <v>78786</v>
+        <v>78791</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1439,48 +1439,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128536490</v>
+        <v>128536758</v>
       </c>
       <c r="B9" t="n">
-        <v>80134</v>
+        <v>92811</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Högflon, Högflon, Jmt</t>
+          <t>Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447202</v>
+        <v>446993</v>
       </c>
       <c r="R9" t="n">
-        <v>6948032</v>
+        <v>6947982</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,60 +1534,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128536758</v>
+        <v>128536490</v>
       </c>
       <c r="B10" t="n">
-        <v>92806</v>
+        <v>80139</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Högflon, Jmt</t>
+          <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446993</v>
+        <v>447202</v>
       </c>
       <c r="R10" t="n">
-        <v>6947982</v>
+        <v>6948032</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,12 +1641,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2007,7 +2007,7 @@
         <v>128536022</v>
       </c>
       <c r="B14" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2345,10 +2345,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128536398</v>
+        <v>128536769</v>
       </c>
       <c r="B17" t="n">
-        <v>92806</v>
+        <v>80168</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2356,21 +2356,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447199</v>
+        <v>446993</v>
       </c>
       <c r="R17" t="n">
-        <v>6948067</v>
+        <v>6948000</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128535206</v>
+        <v>128535194</v>
       </c>
       <c r="B18" t="n">
-        <v>92800</v>
+        <v>78791</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2463,21 +2463,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2493,7 +2493,7 @@
         <v>6948226</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2559,10 +2559,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128536769</v>
+        <v>128536398</v>
       </c>
       <c r="B19" t="n">
-        <v>80163</v>
+        <v>92811</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2570,21 +2570,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2594,10 +2594,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446993</v>
+        <v>447199</v>
       </c>
       <c r="R19" t="n">
-        <v>6948000</v>
+        <v>6948067</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2666,10 +2666,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128535194</v>
+        <v>128535206</v>
       </c>
       <c r="B20" t="n">
-        <v>78786</v>
+        <v>92805</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2677,21 +2677,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2707,7 +2707,7 @@
         <v>6948226</v>
       </c>
       <c r="S20" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2773,10 +2773,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128534979</v>
+        <v>128536454</v>
       </c>
       <c r="B21" t="n">
-        <v>78786</v>
+        <v>80139</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2784,21 +2784,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446445</v>
+        <v>447211</v>
       </c>
       <c r="R21" t="n">
-        <v>6948176</v>
+        <v>6948028</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2868,22 +2868,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128536454</v>
+        <v>128534979</v>
       </c>
       <c r="B22" t="n">
-        <v>80134</v>
+        <v>78791</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2891,21 +2891,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447211</v>
+        <v>446445</v>
       </c>
       <c r="R22" t="n">
-        <v>6948028</v>
+        <v>6948176</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2975,12 +2975,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3457,7 +3457,7 @@
         <v>128537036</v>
       </c>
       <c r="B27" t="n">
-        <v>78786</v>
+        <v>78791</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3795,32 +3795,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128535425</v>
+        <v>128536760</v>
       </c>
       <c r="B30" t="n">
-        <v>92818</v>
+        <v>80139</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4366</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446718</v>
+        <v>446997</v>
       </c>
       <c r="R30" t="n">
-        <v>6948094</v>
+        <v>6947997</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3902,32 +3902,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128536760</v>
+        <v>128535425</v>
       </c>
       <c r="B31" t="n">
-        <v>80134</v>
+        <v>92823</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446997</v>
+        <v>446718</v>
       </c>
       <c r="R31" t="n">
-        <v>6947997</v>
+        <v>6948094</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 16246-2024 artfynd.xlsx
+++ b/artfynd/A 16246-2024 artfynd.xlsx
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128536962</v>
+        <v>128535657</v>
       </c>
       <c r="B7" t="n">
-        <v>78791</v>
+        <v>57723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,34 +1226,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446532</v>
+        <v>446810</v>
       </c>
       <c r="R7" t="n">
-        <v>6948261</v>
+        <v>6948241</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1300,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128535657</v>
+        <v>128536962</v>
       </c>
       <c r="B8" t="n">
-        <v>57723</v>
+        <v>78791</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,39 +1343,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446810</v>
+        <v>446532</v>
       </c>
       <c r="R8" t="n">
-        <v>6948241</v>
+        <v>6948261</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,12 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2004,45 +2004,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128536022</v>
+        <v>128535281</v>
       </c>
       <c r="B14" t="n">
-        <v>92811</v>
+        <v>57723</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447032</v>
+        <v>446670</v>
       </c>
       <c r="R14" t="n">
-        <v>6948185</v>
+        <v>6948128</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2074,7 +2079,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2084,7 +2089,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2111,7 +2121,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128535281</v>
+        <v>128534949</v>
       </c>
       <c r="B15" t="n">
         <v>57723</v>
@@ -2151,10 +2161,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446670</v>
+        <v>446459</v>
       </c>
       <c r="R15" t="n">
-        <v>6948128</v>
+        <v>6948172</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,7 +2196,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2196,7 +2206,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2228,50 +2238,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128534949</v>
+        <v>128536022</v>
       </c>
       <c r="B16" t="n">
-        <v>57723</v>
+        <v>92811</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446459</v>
+        <v>447032</v>
       </c>
       <c r="R16" t="n">
-        <v>6948172</v>
+        <v>6948185</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2303,7 +2308,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2313,12 +2318,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2345,32 +2345,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128536769</v>
+        <v>128535194</v>
       </c>
       <c r="B17" t="n">
-        <v>80168</v>
+        <v>78791</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2380,13 +2380,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446993</v>
+        <v>446523</v>
       </c>
       <c r="R17" t="n">
-        <v>6948000</v>
+        <v>6948226</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2440,44 +2440,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128535194</v>
+        <v>128536398</v>
       </c>
       <c r="B18" t="n">
-        <v>78791</v>
+        <v>92811</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2487,13 +2487,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446523</v>
+        <v>447199</v>
       </c>
       <c r="R18" t="n">
-        <v>6948226</v>
+        <v>6948067</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2547,44 +2547,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128536398</v>
+        <v>128535206</v>
       </c>
       <c r="B19" t="n">
-        <v>92811</v>
+        <v>92805</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2594,13 +2594,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447199</v>
+        <v>446523</v>
       </c>
       <c r="R19" t="n">
-        <v>6948067</v>
+        <v>6948226</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2654,44 +2654,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128535206</v>
+        <v>128536769</v>
       </c>
       <c r="B20" t="n">
-        <v>92805</v>
+        <v>80168</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4362</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2701,13 +2701,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446523</v>
+        <v>446993</v>
       </c>
       <c r="R20" t="n">
-        <v>6948226</v>
+        <v>6948000</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2761,22 +2761,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128536454</v>
+        <v>128534979</v>
       </c>
       <c r="B21" t="n">
-        <v>80139</v>
+        <v>78791</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2784,21 +2784,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447211</v>
+        <v>446445</v>
       </c>
       <c r="R21" t="n">
-        <v>6948028</v>
+        <v>6948176</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2868,22 +2868,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Cecilia  Kreuzberger</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128534979</v>
+        <v>128536454</v>
       </c>
       <c r="B22" t="n">
-        <v>78791</v>
+        <v>80139</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2891,21 +2891,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446445</v>
+        <v>447211</v>
       </c>
       <c r="R22" t="n">
-        <v>6948176</v>
+        <v>6948028</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2975,12 +2975,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia  Kreuzberger</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3795,32 +3795,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128536760</v>
+        <v>128535425</v>
       </c>
       <c r="B30" t="n">
-        <v>80139</v>
+        <v>92823</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446997</v>
+        <v>446718</v>
       </c>
       <c r="R30" t="n">
-        <v>6947997</v>
+        <v>6948094</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3902,32 +3902,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128535425</v>
+        <v>128536760</v>
       </c>
       <c r="B31" t="n">
-        <v>92823</v>
+        <v>80139</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4366</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446718</v>
+        <v>446997</v>
       </c>
       <c r="R31" t="n">
-        <v>6948094</v>
+        <v>6947997</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 16246-2024 artfynd.xlsx
+++ b/artfynd/A 16246-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128535830</v>
       </c>
       <c r="B2" t="n">
-        <v>92805</v>
+        <v>92813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128536458</v>
       </c>
       <c r="B3" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128534788</v>
       </c>
       <c r="B4" t="n">
-        <v>92823</v>
+        <v>92831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>128536951</v>
       </c>
       <c r="B6" t="n">
-        <v>92823</v>
+        <v>92831</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128535657</v>
+        <v>128536962</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>78792</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,39 +1226,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446810</v>
+        <v>446532</v>
       </c>
       <c r="R7" t="n">
-        <v>6948241</v>
+        <v>6948261</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,12 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128536962</v>
+        <v>128535657</v>
       </c>
       <c r="B8" t="n">
-        <v>78791</v>
+        <v>57723</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1343,34 +1333,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Högflon, Högflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446532</v>
+        <v>446810</v>
       </c>
       <c r="R8" t="n">
-        <v>6948261</v>
+        <v>6948241</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1412,7 +1407,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,7 +1442,7 @@
         <v>128536758</v>
       </c>
       <c r="B9" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>128536490</v>
       </c>
       <c r="B10" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>128536022</v>
       </c>
       <c r="B16" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2345,10 +2345,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128535194</v>
+        <v>128535206</v>
       </c>
       <c r="B17" t="n">
-        <v>78791</v>
+        <v>92813</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2356,21 +2356,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2386,7 +2386,7 @@
         <v>6948226</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128536398</v>
+        <v>128536769</v>
       </c>
       <c r="B18" t="n">
-        <v>92811</v>
+        <v>80169</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2463,21 +2463,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447199</v>
+        <v>446993</v>
       </c>
       <c r="R18" t="n">
-        <v>6948067</v>
+        <v>6948000</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2559,10 +2559,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128535206</v>
+        <v>128535194</v>
       </c>
       <c r="B19" t="n">
-        <v>92805</v>
+        <v>78792</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2570,21 +2570,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2600,7 +2600,7 @@
         <v>6948226</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2666,10 +2666,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128536769</v>
+        <v>128536398</v>
       </c>
       <c r="B20" t="n">
-        <v>80168</v>
+        <v>92819</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2677,21 +2677,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446993</v>
+        <v>447199</v>
       </c>
       <c r="R20" t="n">
-        <v>6948000</v>
+        <v>6948067</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2776,7 +2776,7 @@
         <v>128534979</v>
       </c>
       <c r="B21" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>128536454</v>
       </c>
       <c r="B22" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>128537036</v>
       </c>
       <c r="B27" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3795,32 +3795,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128535425</v>
+        <v>128536760</v>
       </c>
       <c r="B30" t="n">
-        <v>92823</v>
+        <v>80140</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4366</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446718</v>
+        <v>446997</v>
       </c>
       <c r="R30" t="n">
-        <v>6948094</v>
+        <v>6947997</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3902,32 +3902,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128536760</v>
+        <v>128535425</v>
       </c>
       <c r="B31" t="n">
-        <v>80139</v>
+        <v>92831</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446997</v>
+        <v>446718</v>
       </c>
       <c r="R31" t="n">
-        <v>6947997</v>
+        <v>6948094</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD31" t="b">
